--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20241201_20250601.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20241201_20250601.xlsx
@@ -1273,37 +1273,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59.83606557377049</v>
+        <v>51.63934426229508</v>
       </c>
       <c r="C20" t="n">
-        <v>40.16393442622951</v>
+        <v>47.54098360655738</v>
       </c>
       <c r="D20" t="n">
-        <v>12.28626054379951</v>
+        <v>31.76525247009594</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>INE090A01021</t>
+          <t>INE704P01025</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>-19.67213114754098</v>
+        <v>-4.098360655737707</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="I20" t="n">
         <v>87</v>
       </c>
       <c r="J20" t="n">
-        <v>1445.8</v>
+        <v>1947.1</v>
       </c>
       <c r="K20" t="n">
         <v>19</v>
@@ -1317,37 +1317,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51.63934426229508</v>
+        <v>56.55737704918032</v>
       </c>
       <c r="C21" t="n">
-        <v>47.54098360655738</v>
+        <v>43.44262295081967</v>
       </c>
       <c r="D21" t="n">
-        <v>31.76525247009594</v>
+        <v>13.65455186084585</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>INE704P01025</t>
+          <t>INE513A01022</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.098360655737707</v>
+        <v>-13.11475409836066</v>
       </c>
       <c r="H21" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21" t="n">
-        <v>1947.1</v>
+        <v>4188.7</v>
       </c>
       <c r="K21" t="n">
         <v>20</v>
